--- a/MSME/BRD - Test Doc/MSME intrim claim calculations.xlsx
+++ b/MSME/BRD - Test Doc/MSME intrim claim calculations.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="1"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Intrim claim(OTS=N)" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="226">
   <si>
     <t>S. No.</t>
   </si>
@@ -538,13 +538,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">Amount recovered through OTS ( Proportionate amount of NCGTC recovery ) – 40% of 9A-9C for MLI / 40% of 9B-9C for NCGTC.
 </t>
     </r>
@@ -561,13 +554,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">Amount recovered through OTS retained by MLI – 60% of 9A-9C for MLI / 60% of 9B-9C for NCGTC.
 </t>
     </r>
@@ -581,6 +567,11 @@
       </rPr>
       <t>NCGTC and MLI portions should be 60% and 40%, respectively, for General MSME, and 75% and 25%, respectively, for Exporter MSME</t>
     </r>
+  </si>
+  <si>
+    <t>Claim amount eligible under scheme
+General MSME - 60%
+Expoter MSME - 75%</t>
   </si>
   <si>
     <t xml:space="preserve">Auto-Calculation  
@@ -3704,14 +3695,14 @@
         <v>44</v>
       </c>
       <c r="F10" s="25">
-        <v>3100000</v>
+        <v>100</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="25">
         <f>F10</f>
-        <v>3100000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:10">
@@ -3732,7 +3723,7 @@
       </c>
       <c r="F11" s="25">
         <f>F10</f>
-        <v>3100000</v>
+        <v>100</v>
       </c>
       <c r="G11" s="26"/>
       <c r="I11" s="31">
@@ -3759,14 +3750,14 @@
         <v>52</v>
       </c>
       <c r="F12" s="25">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="25">
         <f>F12</f>
-        <v>400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3804,14 +3795,14 @@
       </c>
       <c r="F14" s="25">
         <f>IF(F13=1,60%*(F10-F12),75%*(F10-F12))</f>
-        <v>1620000</v>
+        <v>60</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>72</v>
       </c>
       <c r="I14" s="25">
         <f>IF(I13=1,60%*(I10-I12),75%*(I10-I12))</f>
-        <v>1620000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:10">
@@ -3832,14 +3823,14 @@
       </c>
       <c r="F15" s="25">
         <f>IF(F13=1,40%*(F10-F12),25%*(F10-F12))</f>
-        <v>1080000</v>
+        <v>40</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>72</v>
       </c>
       <c r="I15" s="25">
         <f>IF(I13=1,40%*(I10-I12),25%*(I10-I12))</f>
-        <v>1080000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4063,7 +4054,7 @@
       </c>
       <c r="F23" s="25">
         <f>F19+F20-F14</f>
-        <v>298380100</v>
+        <v>300000040</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>72</v>
@@ -4071,10 +4062,10 @@
       <c r="H23" s="36"/>
       <c r="I23" s="25">
         <f>I21+I22-I14</f>
-        <v>398381000</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="1:10">
+        <v>400000940</v>
+      </c>
+    </row>
+    <row r="24" ht="60" spans="1:10">
       <c r="A24" s="7" t="s">
         <v>100</v>
       </c>
@@ -4082,7 +4073,7 @@
         <v>101</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>103</v>
@@ -4091,16 +4082,16 @@
         <v>12</v>
       </c>
       <c r="F24" s="25">
-        <f>75%*(F23-F18)</f>
-        <v>186285075</v>
+        <f>IF(F13=1,60%*F23-F18,75%*F23-F18)</f>
+        <v>130000024</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>72</v>
       </c>
       <c r="H24" s="36"/>
       <c r="I24" s="25">
-        <f>75%*(I23-I18)</f>
-        <v>261285750</v>
+        <f>IF(I13=1,60%*I23-I18,75%*I23-I18)</f>
+        <v>190000564</v>
       </c>
     </row>
     <row r="25" ht="45" spans="1:10">
@@ -4121,7 +4112,7 @@
       </c>
       <c r="F25" s="25">
         <f>IF(F8="N",75%*F24,IF(F8="Y",100%*F24,""))</f>
-        <v>186285075</v>
+        <v>130000024</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>72</v>
@@ -4129,7 +4120,7 @@
       <c r="H25" s="36"/>
       <c r="I25" s="25">
         <f>IF(I8="N",75%*I24,IF(I8="Y",100%*I24,""))</f>
-        <v>261285750</v>
+        <v>190000564</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:10">
@@ -4282,7 +4273,7 @@
         <v>129</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E31" s="24" t="s">
         <v>12</v>
@@ -4397,7 +4388,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4411,7 +4402,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>12</v>
@@ -4427,7 +4418,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>16</v>
@@ -4476,7 +4467,7 @@
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="J5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K5" s="11"/>
     </row>
@@ -4488,7 +4479,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>16</v>
@@ -4499,7 +4490,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="J6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K6" s="12"/>
     </row>
@@ -4508,10 +4499,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>16</v>
@@ -4570,7 +4561,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>43</v>
@@ -4624,10 +4615,10 @@
         <v>54</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>57</v>
@@ -4646,7 +4637,7 @@
         <v>59</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>57</v>
@@ -4665,7 +4656,7 @@
         <v>74</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>16</v>
@@ -4677,7 +4668,7 @@
         <v>100000000</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15">
@@ -4693,10 +4684,10 @@
         <v>77</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>12</v>
@@ -4705,7 +4696,7 @@
         <v>100000000</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16">
@@ -4721,10 +4712,10 @@
         <v>80</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>163</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>162</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>12</v>
@@ -4744,16 +4735,16 @@
         <v>73</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>82</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F18" s="10">
         <v>80000000</v>
@@ -4769,16 +4760,16 @@
         <v>76</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F19" s="10">
         <f>F18</f>
@@ -4795,19 +4786,19 @@
     </row>
     <row r="20" ht="45" spans="1:10">
       <c r="A20" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F20" s="10">
         <f>40%*F18</f>
@@ -4821,19 +4812,19 @@
     </row>
     <row r="21" ht="30" spans="1:10">
       <c r="A21" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F21" s="10">
         <f>60%*F18</f>
@@ -4850,16 +4841,16 @@
         <v>84</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -4869,16 +4860,16 @@
         <v>89</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -4903,7 +4894,7 @@
         <v>50000000</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24">
@@ -4913,10 +4904,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>66</v>
@@ -4942,13 +4933,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>12</v>
@@ -4970,7 +4961,7 @@
         <v>70</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>12</v>
@@ -4991,13 +4982,13 @@
         <v>108</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>12</v>
@@ -5017,13 +5008,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>102</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>12</v>
@@ -5043,10 +5034,10 @@
         <v>116</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>16</v>
@@ -5058,7 +5049,7 @@
         <v>62999995.5</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I30">
         <f t="shared" ref="I30:I35" si="0">F30</f>
@@ -5070,13 +5061,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>12</v>
@@ -5111,7 +5102,7 @@
         <v>5487293.76</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I32">
         <f t="shared" si="0"/>
@@ -5138,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I33">
         <f t="shared" si="0"/>
@@ -5156,7 +5147,7 @@
         <v>118</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>12</v>
@@ -5166,7 +5157,7 @@
         <v>10974587.52</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I34">
         <f t="shared" si="0"/>
@@ -5193,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I35">
         <f t="shared" si="0"/>
@@ -5202,7 +5193,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>124</v>
@@ -5211,7 +5202,7 @@
         <v>124</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>126</v>
@@ -5221,7 +5212,7 @@
         <v>10974587.52</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I36">
         <f>I34-I35</f>
@@ -5230,16 +5221,16 @@
     </row>
     <row r="37" ht="45" spans="1:9">
       <c r="A37" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>128</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>12</v>
@@ -5256,7 +5247,7 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>132</v>
@@ -5265,7 +5256,7 @@
         <v>133</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>12</v>
@@ -5282,7 +5273,7 @@
     </row>
     <row r="39" ht="30" spans="1:9">
       <c r="A39" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>136</v>
@@ -5291,7 +5282,7 @@
         <v>137</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>12</v>
@@ -5354,7 +5345,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>12</v>
@@ -5370,7 +5361,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>16</v>
@@ -5419,7 +5410,7 @@
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="J5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K5" s="11"/>
     </row>
@@ -5431,7 +5422,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>16</v>
@@ -5442,7 +5433,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="J6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K6" s="12"/>
     </row>
@@ -5451,10 +5442,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>16</v>
@@ -5513,7 +5504,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>43</v>
@@ -5567,10 +5558,10 @@
         <v>54</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>57</v>
@@ -5589,7 +5580,7 @@
         <v>59</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>57</v>
@@ -5608,7 +5599,7 @@
         <v>74</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>16</v>
@@ -5620,7 +5611,7 @@
         <v>400000000</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -5632,10 +5623,10 @@
         <v>77</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>12</v>
@@ -5644,7 +5635,7 @@
         <v>5000000</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -5656,10 +5647,10 @@
         <v>80</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>163</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>162</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>12</v>
@@ -5673,16 +5664,16 @@
         <v>73</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>82</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -5692,54 +5683,54 @@
         <v>76</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
     <row r="20" ht="45" spans="1:8">
       <c r="A20" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
     <row r="21" ht="30" spans="1:8">
       <c r="A21" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
@@ -5749,16 +5740,16 @@
         <v>84</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -5768,16 +5759,16 @@
         <v>89</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -5802,16 +5793,16 @@
         <v>150000000</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H24" s="11"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>66</v>
@@ -5833,13 +5824,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>12</v>
@@ -5859,7 +5850,7 @@
         <v>70</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>12</v>
@@ -5876,13 +5867,13 @@
         <v>108</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>12</v>
@@ -5895,13 +5886,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>102</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>12</v>
@@ -5914,10 +5905,10 @@
         <v>116</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>16</v>
@@ -5933,13 +5924,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>12</v>
@@ -5996,7 +5987,7 @@
         <v>118</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>12</v>
@@ -6025,7 +6016,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>124</v>
@@ -6034,7 +6025,7 @@
         <v>124</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>126</v>
@@ -6044,16 +6035,16 @@
     </row>
     <row r="37" ht="45" spans="1:7">
       <c r="A37" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>128</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>12</v>
@@ -6063,7 +6054,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>132</v>
@@ -6072,7 +6063,7 @@
         <v>133</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>12</v>
@@ -6082,7 +6073,7 @@
     </row>
     <row r="39" ht="30" spans="1:7">
       <c r="A39" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>136</v>
@@ -6091,7 +6082,7 @@
         <v>137</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>12</v>
@@ -6117,13 +6108,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:3">
@@ -6131,10 +6122,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:3">
@@ -6142,10 +6133,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="4" ht="30" spans="1:3">
@@ -6153,10 +6144,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" ht="30" spans="1:3">
@@ -6164,10 +6155,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:3">
@@ -6175,10 +6166,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6186,10 +6177,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6197,10 +6188,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6208,10 +6199,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:3">
@@ -6219,10 +6210,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/MSME/BRD - Test Doc/MSME intrim claim calculations.xlsx
+++ b/MSME/BRD - Test Doc/MSME intrim claim calculations.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Intrim claim(OTS=N)" sheetId="3" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Final claim(OTS=N)" sheetId="2" r:id="rId3"/>
     <sheet name="Final claim(OTS=Y)" sheetId="6" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="227">
   <si>
     <t>S. No.</t>
   </si>
@@ -492,10 +493,10 @@
     <t>Amount available for payment against current claim (To Be Paid) – Payment Integration for this amount. This may be part or full payment.</t>
   </si>
   <si>
-    <t>Auto-Calculation  
+    <t xml:space="preserve">Auto-Calculation  
 23 if 23&lt;=28, 
 else 
-28  300&lt;=100</t>
+28  </t>
   </si>
   <si>
     <t>30</t>
@@ -519,7 +520,8 @@
     <t>Carry forward claim pending for previous years</t>
   </si>
   <si>
-    <t>Auto-calc. If 29&lt;23 then 23-29</t>
+    <t>Auto-calc. If 29&lt;23 then 23-29
+else 29</t>
   </si>
   <si>
     <t>Formula MLI side</t>
@@ -538,6 +540,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Amount recovered through OTS ( Proportionate amount of NCGTC recovery ) – 40% of 9A-9C for MLI / 40% of 9B-9C for NCGTC.
 </t>
     </r>
@@ -554,6 +563,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Amount recovered through OTS retained by MLI – 60% of 9A-9C for MLI / 60% of 9B-9C for NCGTC.
 </t>
     </r>
@@ -578,6 +594,9 @@
 23 if 23&lt;=28, 
 else 
 28 </t>
+  </si>
+  <si>
+    <t>Auto-calc. If 29&lt;23 then 23-29</t>
   </si>
   <si>
     <t>Formula for NCGTC</t>
@@ -1890,10 +1909,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2013,9 +2047,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2584,879 +2615,879 @@
   <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="37" customWidth="1"/>
-    <col min="2" max="2" width="38" style="37" customWidth="1"/>
-    <col min="3" max="3" width="64" style="37" customWidth="1"/>
-    <col min="4" max="4" width="48.2857142857143" style="37" customWidth="1"/>
-    <col min="5" max="5" width="25" style="37" customWidth="1"/>
-    <col min="6" max="6" width="21.2857142857143" style="38" customWidth="1"/>
-    <col min="7" max="7" width="16.5714285714286" style="21" customWidth="1"/>
-    <col min="8" max="8" width="21" style="29" customWidth="1"/>
+    <col min="1" max="1" width="6.71428571428571" style="42" customWidth="1"/>
+    <col min="2" max="2" width="38" style="42" customWidth="1"/>
+    <col min="3" max="3" width="64" style="42" customWidth="1"/>
+    <col min="4" max="4" width="48.2857142857143" style="42" customWidth="1"/>
+    <col min="5" max="5" width="25" style="42" customWidth="1"/>
+    <col min="6" max="6" width="21.2857142857143" style="43" customWidth="1"/>
+    <col min="7" max="7" width="16.5714285714286" style="26" customWidth="1"/>
+    <col min="8" max="8" width="21" style="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="45" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="3"/>
+      <c r="E2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" ht="30" spans="1:8">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="42"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="3"/>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="3"/>
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="3"/>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" ht="30" spans="1:8">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="3"/>
+      <c r="E6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" ht="30" spans="1:8">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="3"/>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="46"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="44" t="s">
+      <c r="E8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" ht="30" spans="1:8">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="45" t="s">
+      <c r="E9" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="3"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="46"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="3"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" ht="30" spans="1:8">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="45" t="s">
+      <c r="E11" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="3"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" ht="30" spans="1:8">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="3"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="42">
+      <c r="E13" s="49"/>
+      <c r="F13" s="46">
         <v>1</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="3"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="8"/>
     </row>
     <row r="14" ht="75" spans="1:8">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="51">
         <f>IF(F13=1,60%*(F10-F12),75%*(F10-F12))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="26"/>
-      <c r="H14" s="3"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" ht="75" spans="1:8">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="51">
         <f>IF(F13=1,40%*(F10-F12),25%*(F10-F12))</f>
         <v>0</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="3"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="48">
-        <v>50000000</v>
-      </c>
-      <c r="G16" s="26" t="s">
+      <c r="E16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="52">
+        <v>450000000</v>
+      </c>
+      <c r="G16" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="8">
         <f t="shared" ref="H16:H23" si="0">F16</f>
-        <v>50000000</v>
+        <v>450000000</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="48">
+      <c r="E17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="52">
         <v>1</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:9">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="48">
+      <c r="E18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="52">
         <f>MAX(F16,F17)</f>
+        <v>450000000</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="0"/>
+        <v>450000000</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="1:9">
+      <c r="A19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="52">
         <v>50000000</v>
       </c>
-      <c r="G18" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="G19" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" s="8">
         <f t="shared" si="0"/>
         <v>50000000</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="1:9">
-      <c r="A19" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="43" t="s">
+    <row r="20" ht="30" spans="1:9">
+      <c r="A20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="48">
+      <c r="E20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="52">
+        <v>0</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="30" spans="1:9">
+      <c r="A21" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="52">
+        <v>0</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="30" spans="1:9">
+      <c r="A22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="52">
+        <f>F19</f>
         <v>50000000</v>
       </c>
-      <c r="G19" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" s="3">
+      <c r="G22" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="8">
         <f t="shared" si="0"/>
         <v>50000000</v>
       </c>
-    </row>
-    <row r="20" ht="30" spans="1:9">
-      <c r="A20" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="48">
-        <v>100</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="3">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" ht="30" spans="1:9">
-      <c r="A21" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="48">
+      <c r="I22" s="53" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" ht="30" spans="1:9">
+      <c r="A23" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="52">
+        <f>F20</f>
         <v>0</v>
       </c>
-      <c r="G21" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="G23" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" ht="30" spans="1:9">
-      <c r="A22" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="41" t="s">
+      <c r="I23" s="53" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="1:9">
+      <c r="A24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="48">
-        <f>F19</f>
-        <v>50000000</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="3">
-        <f t="shared" si="0"/>
-        <v>50000000</v>
-      </c>
-      <c r="I22" s="49" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" ht="30" spans="1:9">
-      <c r="A23" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="48">
-        <f>F20</f>
-        <v>100</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="3">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="1:9">
-      <c r="A24" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="52">
         <f>F21</f>
         <v>0</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="8">
         <v>1</v>
       </c>
-      <c r="I24" s="49" t="s">
+      <c r="I24" s="53" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="25" ht="120" spans="1:9">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="48">
+      <c r="E25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="52">
         <f>F19+F20-F21</f>
-        <v>50000100</v>
-      </c>
-      <c r="G25" s="26" t="s">
+        <v>50000000</v>
+      </c>
+      <c r="G25" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H25" s="50">
+      <c r="H25" s="54">
         <f>H22+H23-H24</f>
-        <v>50000099</v>
+        <v>49999999</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:9">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="41" t="s">
+      <c r="D26" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="48">
+      <c r="E26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="52">
         <f>75%*(F25-F18)</f>
-        <v>75</v>
-      </c>
-      <c r="G26" s="26" t="s">
+        <v>-300000000</v>
+      </c>
+      <c r="G26" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="42">
+      <c r="H26" s="46">
         <f>75%*(H25-H18)</f>
-        <v>74.25</v>
+        <v>-300000000.75</v>
       </c>
     </row>
     <row r="27" ht="45" spans="1:9">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="51">
+      <c r="E27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="55">
         <f>IF(F8="N",75%*F26,IF(F8="Y",100%*F26,""))</f>
-        <v>56.25</v>
-      </c>
-      <c r="G27" s="33" t="s">
+        <v>-225000000</v>
+      </c>
+      <c r="G27" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="52">
+      <c r="H27" s="56">
         <f>F27</f>
-        <v>56.25</v>
+        <v>-225000000</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="43" t="s">
+      <c r="D28" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="48">
+      <c r="E28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="52">
         <v>26550000</v>
       </c>
-      <c r="G28" s="26" t="s">
+      <c r="G28" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="8">
         <f>F28</f>
         <v>26550000</v>
       </c>
     </row>
     <row r="29" ht="45" spans="1:9">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="43" t="s">
+      <c r="D29" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="48">
+      <c r="E29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="52">
         <v>0</v>
       </c>
-      <c r="G29" s="26" t="s">
+      <c r="G29" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="8">
         <f>F29</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="30" spans="1:9">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="41" t="s">
+      <c r="D30" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="48">
+      <c r="E30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="52">
         <f>3*(F28+F29)</f>
         <v>79650000</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H30" s="42">
+      <c r="H30" s="46">
         <f>3*(H28+H29)</f>
         <v>79650000</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:9">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="E31" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="48">
+      <c r="E31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="52">
         <v>0</v>
       </c>
-      <c r="G31" s="26"/>
-      <c r="H31" s="3">
+      <c r="G31" s="31"/>
+      <c r="H31" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="C32" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="41" t="s">
+      <c r="D32" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="41" t="s">
+      <c r="E32" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="48">
+      <c r="F32" s="52">
         <f>F30-F31</f>
         <v>79650000</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H32" s="42">
+      <c r="H32" s="46">
         <f>H30-H31</f>
         <v>79650000</v>
       </c>
     </row>
     <row r="33" ht="60" spans="1:8">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D33" s="41" t="s">
+      <c r="D33" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E33" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="51">
+      <c r="E33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="55">
         <f>IF(F27&lt;=F32,F27,F32)</f>
-        <v>56.25</v>
-      </c>
-      <c r="G33" s="26" t="s">
+        <v>-225000000</v>
+      </c>
+      <c r="G33" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H33" s="54">
+      <c r="H33" s="58">
         <f>IF(H27&lt;=H32,H27,H32)</f>
-        <v>56.25</v>
+        <v>-225000000</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="41" t="s">
+      <c r="D34" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E34" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="51">
+      <c r="E34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="55">
         <f>F32-F33</f>
-        <v>79649943.75</v>
-      </c>
-      <c r="G34" s="33" t="s">
+        <v>304650000</v>
+      </c>
+      <c r="G34" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="H34" s="54">
+      <c r="H34" s="58">
         <f>H32-H33</f>
-        <v>79649943.75</v>
+        <v>304650000</v>
       </c>
     </row>
     <row r="35" ht="30" spans="1:8">
-      <c r="A35" s="41" t="s">
+      <c r="A35" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C35" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="41" t="s">
+      <c r="D35" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="E35" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="48" t="b">
+      <c r="E35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="52" t="b">
         <f>IF(F33&lt;F27,F27-F33)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H35" s="3"/>
+      <c r="H35" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3470,878 +3501,878 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.4190476190476" style="18" customWidth="1"/>
-    <col min="2" max="2" width="38" style="19" customWidth="1"/>
-    <col min="3" max="3" width="64" style="19" customWidth="1"/>
-    <col min="4" max="4" width="39.6571428571429" style="19" customWidth="1"/>
-    <col min="5" max="5" width="34.2857142857143" style="19" customWidth="1"/>
-    <col min="6" max="6" width="21.2857142857143" style="20" customWidth="1"/>
-    <col min="7" max="7" width="16.5714285714286" style="21" customWidth="1"/>
-    <col min="8" max="8" width="9.4" style="22" customWidth="1"/>
-    <col min="9" max="9" width="21.2857142857143" style="20" customWidth="1"/>
-    <col min="10" max="16384" width="9.14285714285714" style="22"/>
+    <col min="1" max="1" width="10.4190476190476" style="23" customWidth="1"/>
+    <col min="2" max="2" width="38" style="24" customWidth="1"/>
+    <col min="3" max="3" width="64" style="24" customWidth="1"/>
+    <col min="4" max="4" width="39.6571428571429" style="24" customWidth="1"/>
+    <col min="5" max="5" width="34.2857142857143" style="24" customWidth="1"/>
+    <col min="6" max="6" width="21.2857142857143" style="25" customWidth="1"/>
+    <col min="7" max="7" width="16.5714285714286" style="26" customWidth="1"/>
+    <col min="8" max="8" width="9.4" style="27" customWidth="1"/>
+    <col min="9" max="9" width="21.2857142857143" style="25" customWidth="1"/>
+    <col min="10" max="16384" width="9.14285714285714" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="28" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26"/>
-      <c r="I2" s="25"/>
+      <c r="E2" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="30"/>
+      <c r="G2" s="31"/>
+      <c r="I2" s="30"/>
     </row>
     <row r="3" ht="30" spans="1:10">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="25"/>
-      <c r="G3" s="26"/>
-      <c r="I3" s="25"/>
+      <c r="E3" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="26"/>
-      <c r="I4" s="25"/>
+      <c r="E4" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="30"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="25"/>
-      <c r="G5" s="26"/>
-      <c r="I5" s="25"/>
+      <c r="E5" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="31"/>
+      <c r="I5" s="30"/>
     </row>
     <row r="6" ht="30" spans="1:10">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
-      <c r="I6" s="25"/>
+      <c r="E6" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="30"/>
+      <c r="G6" s="31"/>
+      <c r="I6" s="30"/>
     </row>
     <row r="7" ht="30" spans="1:10">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="26"/>
-      <c r="I7" s="25"/>
+      <c r="E7" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31"/>
+      <c r="I7" s="30"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="28" t="s">
+      <c r="E8" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="29"/>
-      <c r="I8" s="28" t="str">
+      <c r="H8" s="34"/>
+      <c r="I8" s="33" t="str">
         <f>F8</f>
         <v>Y</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:10">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="26" t="s">
+      <c r="F9" s="30"/>
+      <c r="G9" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="25"/>
+      <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="30">
         <v>100</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="30">
         <f>F10</f>
         <v>100</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:10">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="30">
         <f>F10</f>
         <v>100</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="I11" s="31">
+      <c r="G11" s="31"/>
+      <c r="I11" s="36">
         <v>4100000</v>
       </c>
-      <c r="J11" s="32" t="s">
+      <c r="J11" s="37" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="12" ht="30" spans="1:10">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="30">
         <v>0</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="30">
         <f>F12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="7"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="30" t="s">
+      <c r="A13" s="12"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="38">
         <v>1</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="I13" s="33">
+      <c r="G13" s="31"/>
+      <c r="I13" s="38">
         <f>F13</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="75" spans="1:10">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="30">
         <f>IF(F13=1,60%*(F10-F12),75%*(F10-F12))</f>
         <v>60</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="30">
         <f>IF(I13=1,60%*(I10-I12),75%*(I10-I12))</f>
         <v>60</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:10">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="30">
         <f>IF(F13=1,40%*(F10-F12),25%*(F10-F12))</f>
         <v>40</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="30">
         <f>IF(I13=1,40%*(I10-I12),25%*(I10-I12))</f>
         <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="25">
+      <c r="E16" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="30">
         <v>50000000</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="25">
+      <c r="H16" s="39"/>
+      <c r="I16" s="30">
         <f>F16</f>
         <v>50000000</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="31">
+      <c r="E17" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="36">
         <v>1</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="34"/>
-      <c r="I17" s="31">
+      <c r="H17" s="39"/>
+      <c r="I17" s="36">
         <f>F17</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="25">
+      <c r="E18" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="30">
         <f>MAX(F16,F17)</f>
         <v>50000000</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="G18" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="34"/>
-      <c r="I18" s="25">
+      <c r="H18" s="39"/>
+      <c r="I18" s="30">
         <f>MAX(I16,I17)</f>
         <v>50000000</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="25">
+      <c r="E19" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="30">
         <v>300000000</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="25">
+      <c r="H19" s="39"/>
+      <c r="I19" s="30">
         <f>F19</f>
         <v>300000000</v>
       </c>
     </row>
     <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="25">
+      <c r="E20" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="30">
         <v>100</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="25">
+      <c r="H20" s="39"/>
+      <c r="I20" s="30">
         <f>F20</f>
         <v>100</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="E21" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="25">
+      <c r="E21" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="30">
         <f>F19</f>
         <v>300000000</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="35"/>
-      <c r="I21" s="31">
+      <c r="H21" s="40"/>
+      <c r="I21" s="36">
         <v>400000000</v>
       </c>
-      <c r="J21" s="32" t="s">
+      <c r="J21" s="37" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:10">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="25">
+      <c r="E22" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="30">
         <f>F20</f>
         <v>100</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H22" s="35"/>
-      <c r="I22" s="31">
+      <c r="H22" s="40"/>
+      <c r="I22" s="36">
         <v>1000</v>
       </c>
-      <c r="J22" s="32" t="s">
+      <c r="J22" s="37" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="23" ht="120" spans="1:10">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="25">
+      <c r="E23" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="30">
         <f>F19+F20-F14</f>
         <v>300000040</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="25">
+      <c r="H23" s="41"/>
+      <c r="I23" s="30">
         <f>I21+I22-I14</f>
         <v>400000940</v>
       </c>
     </row>
     <row r="24" ht="60" spans="1:10">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="25">
+      <c r="E24" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="30">
         <f>IF(F13=1,60%*F23-F18,75%*F23-F18)</f>
         <v>130000024</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="25">
+      <c r="H24" s="41"/>
+      <c r="I24" s="30">
         <f>IF(I13=1,60%*I23-I18,75%*I23-I18)</f>
         <v>190000564</v>
       </c>
     </row>
     <row r="25" ht="45" spans="1:10">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="25">
+      <c r="E25" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="30">
         <f>IF(F8="N",75%*F24,IF(F8="Y",100%*F24,""))</f>
         <v>130000024</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="25">
+      <c r="H25" s="41"/>
+      <c r="I25" s="30">
         <f>IF(I8="N",75%*I24,IF(I8="Y",100%*I24,""))</f>
         <v>190000564</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:10">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="25">
+      <c r="E26" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="30">
         <v>26550000</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G26" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="H26" s="36"/>
-      <c r="I26" s="25">
+      <c r="H26" s="41"/>
+      <c r="I26" s="30">
         <f>F26</f>
         <v>26550000</v>
       </c>
     </row>
     <row r="27" ht="45" spans="1:10">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="25">
+      <c r="E27" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="30">
         <v>0</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="H27" s="36"/>
-      <c r="I27" s="25">
+      <c r="H27" s="41"/>
+      <c r="I27" s="30">
         <f>F27</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:10">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="E28" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="25">
+      <c r="E28" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="30">
         <f>3*(F26+F27)</f>
         <v>79650000</v>
       </c>
-      <c r="G28" s="26" t="s">
+      <c r="G28" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H28" s="36"/>
-      <c r="I28" s="25">
+      <c r="H28" s="41"/>
+      <c r="I28" s="30">
         <f>3*(I26+I27)</f>
         <v>79650000</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:10">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E29" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="31">
+      <c r="E29" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="36">
         <v>0</v>
       </c>
-      <c r="G29" s="26"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="31">
+      <c r="G29" s="31"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="30">
         <f>F28-F29</f>
         <v>79650000</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H30" s="36"/>
-      <c r="I30" s="25">
+      <c r="H30" s="41"/>
+      <c r="I30" s="30">
         <f>I28-I29</f>
         <v>79650000</v>
       </c>
     </row>
     <row r="31" ht="60" spans="1:10">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="E31" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="25">
+      <c r="E31" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="30">
         <f>IF(F25&lt;=F30,F25,F30)</f>
         <v>79650000</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="G31" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H31" s="36"/>
-      <c r="I31" s="25">
+      <c r="H31" s="41"/>
+      <c r="I31" s="30">
         <f>IF(I25&lt;=I30,I25,I30)</f>
         <v>79650000</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:10">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="25">
+      <c r="E32" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="30">
         <f>F30-F31</f>
         <v>0</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H32" s="36"/>
-      <c r="I32" s="25">
+      <c r="H32" s="41"/>
+      <c r="I32" s="30">
         <f>I30-I31</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:9">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="D33" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="25"/>
-      <c r="G33" s="26" t="s">
+      <c r="D33" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="30"/>
+      <c r="G33" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H33" s="36"/>
-      <c r="I33" s="25"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4355,427 +4386,427 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="5" customWidth="1"/>
-    <col min="2" max="2" width="42.5714285714286" style="5" customWidth="1"/>
-    <col min="3" max="3" width="49.1428571428571" style="5" customWidth="1"/>
-    <col min="4" max="4" width="42.2857142857143" style="5" customWidth="1"/>
-    <col min="5" max="5" width="31.4285714285714" style="5" customWidth="1"/>
-    <col min="6" max="6" width="27.2857142857143" style="6" customWidth="1"/>
-    <col min="7" max="7" width="20.8571428571429" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.71428571428571" style="10" customWidth="1"/>
+    <col min="2" max="2" width="42.5714285714286" style="10" customWidth="1"/>
+    <col min="3" max="3" width="49.1428571428571" style="10" customWidth="1"/>
+    <col min="4" max="4" width="42.2857142857143" style="10" customWidth="1"/>
+    <col min="5" max="5" width="31.4285714285714" style="10" customWidth="1"/>
+    <col min="6" max="6" width="27.2857142857143" style="11" customWidth="1"/>
+    <col min="7" max="7" width="20.8571428571429" style="11" customWidth="1"/>
     <col min="9" max="9" width="24.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>148</v>
+      <c r="I1" s="13" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="D2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" ht="30" spans="1:11">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="E3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="E4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="E5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
       <c r="J5" t="s">
-        <v>151</v>
-      </c>
-      <c r="K5" s="11"/>
+        <v>152</v>
+      </c>
+      <c r="K5" s="16"/>
     </row>
     <row r="6" ht="75" spans="1:11">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
+      <c r="E6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
       <c r="J6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K6" s="12"/>
+        <v>154</v>
+      </c>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" ht="45" spans="1:11">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="C7" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="E7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
+      <c r="E8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" ht="30" spans="1:11">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="C10" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
     </row>
     <row r="11" ht="45" spans="1:11">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="E12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
     </row>
     <row r="13" ht="45" spans="1:11">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="C13" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" ht="30" spans="1:11">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="C14" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
     </row>
     <row r="15" ht="60" spans="1:11">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="E15" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="15">
         <v>100000000</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H15" s="11"/>
+      <c r="G15" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="H15" s="16"/>
       <c r="I15">
         <f>F15</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="16" ht="45" spans="1:11">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="15">
+        <v>100000000</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="11"/>
+      <c r="H16" s="16"/>
       <c r="I16">
         <f>F16</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="10">
+      <c r="E17" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="15">
         <v>10</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
       <c r="I17">
         <f>F17</f>
         <v>10</v>
       </c>
     </row>
     <row r="18" ht="45" spans="1:10">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F18" s="10">
+      <c r="E18" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" s="15">
         <v>80000000</v>
       </c>
-      <c r="G18" s="10"/>
+      <c r="G18" s="15"/>
       <c r="I18">
         <f>F18</f>
         <v>80000000</v>
       </c>
     </row>
     <row r="19" ht="45" spans="1:10">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="E19" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F19" s="15">
         <f>F18</f>
         <v>80000000</v>
       </c>
-      <c r="G19" s="10"/>
+      <c r="G19" s="15"/>
       <c r="I19">
         <f>F19</f>
         <v>80000000</v>
@@ -4785,271 +4816,271 @@
       </c>
     </row>
     <row r="20" ht="45" spans="1:10">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="F20" s="15">
         <f>40%*F18</f>
         <v>32000000</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="15"/>
       <c r="I20">
         <f>40%*I19</f>
         <v>32000000</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="A21" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="B21" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="C21" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F21" s="10">
+      <c r="E21" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F21" s="15">
         <f>60%*F18</f>
         <v>48000000</v>
       </c>
-      <c r="G21" s="10"/>
+      <c r="G21" s="15"/>
       <c r="I21">
         <f>60%*I19</f>
         <v>48000000</v>
       </c>
     </row>
     <row r="22" ht="60" spans="1:10">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="C22" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="D22" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="E22" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="C23" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
+      <c r="E23" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="10">
+      <c r="E24" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="15">
         <v>50000000</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="H24" s="11"/>
+      <c r="G24" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="16"/>
       <c r="I24">
         <f>F24</f>
         <v>50000000</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="9" t="s">
+      <c r="A25" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="B25" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="E25" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="14">
         <v>60000000</v>
       </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="11"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
       <c r="I25">
         <f>F25</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="B26" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="C26" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="10">
+      <c r="D26" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="15">
         <v>1</v>
       </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="11"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" ht="30" spans="1:10">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="10">
+      <c r="D27" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="15">
         <f>MAX(F24,F25)</f>
         <v>60000000</v>
       </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="11"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16"/>
       <c r="I27">
         <f>F27</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="28" ht="120" spans="1:10">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="B28" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="10">
+      <c r="C28" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="15">
         <f>F15+F16-F17-F20</f>
         <v>167999990</v>
       </c>
-      <c r="G28" s="10"/>
+      <c r="G28" s="15"/>
       <c r="I28">
         <f>I15+I16-I17-I20</f>
         <v>167999990</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:10">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="B29" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="10">
+      <c r="D29" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="15">
         <f>60%*(F28-F27)</f>
         <v>64799994</v>
       </c>
-      <c r="G29" s="10"/>
+      <c r="G29" s="15"/>
       <c r="I29">
         <f>60%*(I28-I27)</f>
         <v>64799994</v>
       </c>
     </row>
     <row r="30" ht="30" spans="1:10">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="B30" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="C30" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="17">
+      <c r="E30" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="22">
         <v>62999995.5</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>184</v>
+      <c r="G30" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="I30">
         <f t="shared" ref="I30:I35" si="0">F30</f>
@@ -5057,52 +5088,52 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="B31" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="C31" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="10">
+      <c r="D31" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="15">
         <f>F29-F30</f>
         <v>1799998.5</v>
       </c>
-      <c r="G31" s="10"/>
+      <c r="G31" s="15"/>
       <c r="I31">
         <f t="shared" si="0"/>
         <v>1799998.5</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:10">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="10">
+      <c r="E32" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="15">
         <v>5487293.76</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>184</v>
+      <c r="G32" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="I32">
         <f t="shared" si="0"/>
@@ -5110,26 +5141,26 @@
       </c>
     </row>
     <row r="33" ht="30" spans="1:9">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="10">
+      <c r="E33" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="15">
         <v>0</v>
       </c>
-      <c r="G33" s="10" t="s">
-        <v>184</v>
+      <c r="G33" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="I33">
         <f t="shared" si="0"/>
@@ -5137,27 +5168,27 @@
       </c>
     </row>
     <row r="34" ht="30" spans="1:9">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="10">
+      <c r="D34" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="15">
         <f>2*(F33+F32)</f>
         <v>10974587.52</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>201</v>
+      <c r="G34" s="15" t="s">
+        <v>202</v>
       </c>
       <c r="I34">
         <f t="shared" si="0"/>
@@ -5165,26 +5196,26 @@
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="10">
+      <c r="E35" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="15">
         <v>0</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>184</v>
+      <c r="G35" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="I35">
         <f t="shared" si="0"/>
@@ -5192,27 +5223,27 @@
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E36" s="9" t="s">
+      <c r="D36" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F34-F35</f>
         <v>10974587.52</v>
       </c>
-      <c r="G36" s="10" t="s">
-        <v>201</v>
+      <c r="G36" s="15" t="s">
+        <v>202</v>
       </c>
       <c r="I36">
         <f>I34-I35</f>
@@ -5220,75 +5251,75 @@
       </c>
     </row>
     <row r="37" ht="45" spans="1:9">
-      <c r="A37" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="C37" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="10">
+      <c r="D37" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="15">
         <f>IF(F31&lt;=F36,F31,F36)</f>
         <v>1799998.5</v>
       </c>
-      <c r="G37" s="10"/>
-      <c r="I37" s="10">
+      <c r="G37" s="15"/>
+      <c r="I37" s="15">
         <f>IF(I31&lt;=I36,I31,I36)</f>
         <v>1799998.5</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B38" s="9" t="s">
+      <c r="A38" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="10">
+      <c r="D38" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="15">
         <f>F36-F37</f>
         <v>9174589.02</v>
       </c>
-      <c r="G38" s="10"/>
-      <c r="I38" s="10">
+      <c r="G38" s="15"/>
+      <c r="I38" s="15">
         <f>I36-I37</f>
         <v>9174589.02</v>
       </c>
     </row>
     <row r="39" ht="30" spans="1:9">
-      <c r="A39" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B39" s="9" t="s">
+      <c r="A39" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
+      <c r="D39" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5302,793 +5333,793 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="5" customWidth="1"/>
-    <col min="2" max="2" width="42.5714285714286" style="5" customWidth="1"/>
-    <col min="3" max="3" width="49.1428571428571" style="5" customWidth="1"/>
-    <col min="4" max="4" width="42.2857142857143" style="5" customWidth="1"/>
-    <col min="5" max="5" width="31.4285714285714" style="5" customWidth="1"/>
-    <col min="6" max="6" width="27.2857142857143" style="6" customWidth="1"/>
-    <col min="7" max="7" width="20.8571428571429" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.71428571428571" style="10" customWidth="1"/>
+    <col min="2" max="2" width="42.5714285714286" style="10" customWidth="1"/>
+    <col min="3" max="3" width="49.1428571428571" style="10" customWidth="1"/>
+    <col min="4" max="4" width="42.2857142857143" style="10" customWidth="1"/>
+    <col min="5" max="5" width="31.4285714285714" style="10" customWidth="1"/>
+    <col min="6" max="6" width="27.2857142857143" style="11" customWidth="1"/>
+    <col min="7" max="7" width="20.8571428571429" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="D2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" ht="30" spans="1:11">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="E3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="E4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="E5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
       <c r="J5" t="s">
-        <v>151</v>
-      </c>
-      <c r="K5" s="11"/>
+        <v>152</v>
+      </c>
+      <c r="K5" s="16"/>
     </row>
     <row r="6" ht="75" spans="1:11">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
+      <c r="E6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
       <c r="J6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K6" s="12"/>
+        <v>154</v>
+      </c>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" ht="45" spans="1:11">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="C7" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="E7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
+      <c r="E8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" ht="30" spans="1:11">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="C10" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
     </row>
     <row r="11" ht="45" spans="1:11">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="E12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
     </row>
     <row r="13" ht="45" spans="1:11">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="C13" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" ht="30" spans="1:11">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="C14" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
     </row>
     <row r="15" ht="60" spans="1:11">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="E15" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="15">
         <v>400000000</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H15" s="11"/>
+      <c r="G15" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" ht="45" spans="1:11">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="15">
+        <v>5000000</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="10">
-        <v>5000000</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="11"/>
+      <c r="H16" s="16"/>
     </row>
     <row r="17" ht="30" spans="1:8">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
+      <c r="E17" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
     </row>
     <row r="18" ht="45" spans="1:8">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
+      <c r="E18" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" ht="45" spans="1:8">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
+      <c r="E19" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" ht="45" spans="1:8">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+    </row>
+    <row r="21" ht="30" spans="1:8">
+      <c r="A21" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-    </row>
-    <row r="21" ht="30" spans="1:8">
-      <c r="A21" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="E21" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
     </row>
     <row r="22" ht="60" spans="1:8">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="C22" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="D22" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="E22" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="C23" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
+      <c r="E23" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="10">
+      <c r="E24" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="15">
         <v>150000000</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="H24" s="11"/>
+      <c r="G24" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="9" t="s">
+      <c r="A25" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="B25" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="10">
+      <c r="E25" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="15">
         <v>150000001</v>
       </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="11"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="B26" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="C26" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="11"/>
+      <c r="D26" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" ht="30" spans="1:8">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="10">
+      <c r="D27" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="15">
         <f>MAX(F24,F25)</f>
         <v>150000001</v>
       </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="11"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" ht="120" spans="1:8">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="B28" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
+      <c r="C28" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" ht="30" spans="1:8">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="B29" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
+      <c r="D29" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" ht="30" spans="1:8">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="B30" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="C30" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
+      <c r="E30" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="B31" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="C31" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
+      <c r="D31" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" ht="30" spans="1:8">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
+      <c r="E32" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33" ht="30" spans="1:7">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
+      <c r="E33" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" ht="30" spans="1:7">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
+      <c r="D34" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
+      <c r="E35" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E36" s="9" t="s">
+      <c r="D36" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
     </row>
     <row r="37" ht="45" spans="1:7">
-      <c r="A37" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="C37" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+      <c r="D37" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B38" s="9" t="s">
+      <c r="A38" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
+      <c r="D38" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
     </row>
     <row r="39" ht="30" spans="1:7">
-      <c r="A39" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B39" s="9" t="s">
+      <c r="A39" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
+      <c r="D39" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6099,7 +6130,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="82.2857142857143" customWidth="1"/>
@@ -6107,114 +6138,175 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>213</v>
       </c>
+      <c r="C1" s="7" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="2" ht="30" spans="1:3">
-      <c r="A2" s="3">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="9" t="s">
         <v>215</v>
       </c>
+      <c r="C2" s="9" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="3" ht="30" spans="1:3">
-      <c r="A3" s="3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="4" ht="30" spans="1:3">
-      <c r="A4" s="3">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="9" t="s">
         <v>218</v>
       </c>
+      <c r="C4" s="9" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="5" ht="30" spans="1:3">
-      <c r="A5" s="3">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>215</v>
+      <c r="B5" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:3">
-      <c r="A6" s="3">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>215</v>
+      <c r="B6" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>215</v>
+      <c r="B7" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>215</v>
+      <c r="B8" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>215</v>
+      <c r="B9" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:3">
-      <c r="A10" s="3">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>225</v>
       </c>
+      <c r="C10" s="9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" ht="30" spans="2:3">
+      <c r="B17" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="9.14285714285714" style="1"/>
+    <col min="2" max="2" width="33.4285714285714" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5714285714286" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.4285714285714" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.14285714285714" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="45" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" customFormat="1" ht="45" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
